--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,11 @@
           <t>logged_at</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_volume</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -535,6 +540,7 @@
           <t>2026-01-02 21:06:53</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,6 +587,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,6 +634,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -673,6 +681,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,6 +728,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -765,6 +775,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,6 +822,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -857,6 +869,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -903,6 +916,7 @@
           <t>2026-01-02 21:08:57</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,6 +962,56 @@
         <is>
           <t>2026-01-02 21:08:57</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E12" t="n">
+        <v>438.0700073242188</v>
+      </c>
+      <c r="F12" t="n">
+        <v>434.2655477364987</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.8684592700052904</v>
+      </c>
+      <c r="H12" t="n">
+        <v>440</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4021666229248047</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4958914869376754</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-01-03 18:49:11</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>85263000</v>
       </c>
     </row>
   </sheetData>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,496 @@
         <v>85263000</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E13" t="n">
+        <v>432.9599914550781</v>
+      </c>
+      <c r="F13" t="n">
+        <v>430.2022625936588</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.6369477355520131</v>
+      </c>
+      <c r="H13" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4242000939941406</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5234431461861282</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>88816200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>262.3599853515625</v>
+      </c>
+      <c r="F14" t="n">
+        <v>264.6481119034572</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8721324438361181</v>
+      </c>
+      <c r="H14" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2290116162109375</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5082214689724482</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>52282100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>478.510009765625</v>
+      </c>
+      <c r="F15" t="n">
+        <v>466.7616712047534</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2.455191808135</v>
+      </c>
+      <c r="H15" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2212602288818359</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5402074294374107</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>23007300</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>240.9299926757812</v>
+      </c>
+      <c r="F16" t="n">
+        <v>242.1803188623138</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5189582968256943</v>
+      </c>
+      <c r="H16" t="n">
+        <v>240</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2846751220703124</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5510995658280795</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>53667800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>314.3399963378906</v>
+      </c>
+      <c r="F17" t="n">
+        <v>315.1937354390649</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2715973503596258</v>
+      </c>
+      <c r="H17" t="n">
+        <v>315</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2851023638916015</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4948098586471923</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>31178900</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>660.6199951171875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>659.9683551650631</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.09864066436692717</v>
+      </c>
+      <c r="H18" t="n">
+        <v>660</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2634351000976562</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.524095410462773</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>11054900</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>187.2400054931641</v>
+      </c>
+      <c r="F19" t="n">
+        <v>98.56279652053405</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-47.36018285145133</v>
+      </c>
+      <c r="H19" t="n">
+        <v>187</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3949035119628906</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.5248848581587817</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>176174700</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>334.6099853515625</v>
+      </c>
+      <c r="F20" t="n">
+        <v>335.7291668029859</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.334473416938684</v>
+      </c>
+      <c r="H20" t="n">
+        <v>335</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3186103295898437</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5051176014538967</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>7657900</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19.56999969482422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21.29766194928189</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.828115898819322</v>
+      </c>
+      <c r="H21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.016606479492188</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5411891170397287</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>51253400</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E22" t="n">
+        <v>95.59999847412109</v>
+      </c>
+      <c r="F22" t="n">
+        <v>96.46277876581044</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9024898592680436</v>
+      </c>
+      <c r="H22" t="n">
+        <v>96</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.020512709960938</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.5208382701120902</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-01-07 03:54:21</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>20066600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,496 @@
         <v>20066600</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E23" t="n">
+        <v>445.010009765625</v>
+      </c>
+      <c r="F23" t="n">
+        <v>439.6336978104062</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.208132814372054</v>
+      </c>
+      <c r="H23" t="n">
+        <v>445</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.374456939086914</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.5186465690935784</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>67185700</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E24" t="n">
+        <v>259.3699951171875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>249.5669942094937</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.779543159286653</v>
+      </c>
+      <c r="H24" t="n">
+        <v>260</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2254716125488281</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.4922963637439793</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>39952300</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E25" t="n">
+        <v>479.2799987792969</v>
+      </c>
+      <c r="F25" t="n">
+        <v>477.3044887678043</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.4121828610674589</v>
+      </c>
+      <c r="H25" t="n">
+        <v>480</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2050250396728515</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5004078719677464</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>18484000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E26" t="n">
+        <v>247.3800048828125</v>
+      </c>
+      <c r="F26" t="n">
+        <v>248.5048395305622</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4546990967530015</v>
+      </c>
+      <c r="H26" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.259345785522461</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5126927274067057</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>34534700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E27" t="n">
+        <v>328.5700073242188</v>
+      </c>
+      <c r="F27" t="n">
+        <v>327.6704938235229</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.2737661626577765</v>
+      </c>
+      <c r="H27" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2692944165039062</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.5447815876208922</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>26183500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E28" t="n">
+        <v>653.0599975585938</v>
+      </c>
+      <c r="F28" t="n">
+        <v>631.0194667493756</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-3.374962620833411</v>
+      </c>
+      <c r="H28" t="n">
+        <v>652.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.255714230041504</v>
+      </c>
+      <c r="J28" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.5246737000845987</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>11621500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E29" t="n">
+        <v>184.8600006103516</v>
+      </c>
+      <c r="F29" t="n">
+        <v>184.2030172549561</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.3553950845105842</v>
+      </c>
+      <c r="H29" t="n">
+        <v>185</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3474186352539062</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.5130009963103713</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>131072000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E30" t="n">
+        <v>329.1900024414062</v>
+      </c>
+      <c r="F30" t="n">
+        <v>324.8286402021619</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.324876881709257</v>
+      </c>
+      <c r="H30" t="n">
+        <v>330</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.3082344567871094</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.4990918331739833</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>6735300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20.51000022888184</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19.95016542576044</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-2.729569950628493</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.067387475585938</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.5398915204422353</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>51227900</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E32" t="n">
+        <v>105.3099975585938</v>
+      </c>
+      <c r="F32" t="n">
+        <v>104.4442703673074</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.8220750274015103</v>
+      </c>
+      <c r="H32" t="n">
+        <v>105</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.017583037109375</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.543847827478549</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:38:24</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>33864400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +1994,496 @@
         <v>33864400</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E33" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>438.7916735229269</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.295239662383301</v>
+      </c>
+      <c r="H33" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.503056727294922</v>
+      </c>
+      <c r="J33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.5215396109541164</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>60047300</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E34" t="n">
+        <v>255.5299987792969</v>
+      </c>
+      <c r="F34" t="n">
+        <v>251.4532001976386</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-1.595428560691023</v>
+      </c>
+      <c r="H34" t="n">
+        <v>255</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3220282641601562</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.5323841539484803</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>72018600</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E35" t="n">
+        <v>459.8599853515625</v>
+      </c>
+      <c r="F35" t="n">
+        <v>435.4530710848546</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-5.307466412423079</v>
+      </c>
+      <c r="H35" t="n">
+        <v>460</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3948424774169922</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.5171576588633342</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>33795700</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E36" t="n">
+        <v>239.1199951171875</v>
+      </c>
+      <c r="F36" t="n">
+        <v>230.4358478909062</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-3.631711025263876</v>
+      </c>
+      <c r="H36" t="n">
+        <v>240</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2843089147949218</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.4874629383663465</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>45824700</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E37" t="n">
+        <v>330</v>
+      </c>
+      <c r="F37" t="n">
+        <v>330.7801954140724</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.2364228527491977</v>
+      </c>
+      <c r="H37" t="n">
+        <v>330</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.293830303955078</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.5172405081779715</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>40250800</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E38" t="n">
+        <v>620.25</v>
+      </c>
+      <c r="F38" t="n">
+        <v>618.1584643461509</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.3372084891332631</v>
+      </c>
+      <c r="H38" t="n">
+        <v>620</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4975941354370118</v>
+      </c>
+      <c r="J38" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.5232549365213253</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>16869800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E39" t="n">
+        <v>186.2299957275391</v>
+      </c>
+      <c r="F39" t="n">
+        <v>186.1061975353004</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.06647596793148149</v>
+      </c>
+      <c r="H39" t="n">
+        <v>185</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3815979809570312</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.5583558274416951</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>187613900</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E40" t="n">
+        <v>312.4700012207031</v>
+      </c>
+      <c r="F40" t="n">
+        <v>322.5807436054664</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.235748182310093</v>
+      </c>
+      <c r="H40" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2301712725830078</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.5160343406493733</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>14637600</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20.19000053405762</v>
+      </c>
+      <c r="F41" t="n">
+        <v>20.52994404106709</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.683722129853505</v>
+      </c>
+      <c r="H41" t="n">
+        <v>20</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.004887788085937</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.5582790348285847</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>34785200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E42" t="n">
+        <v>94.94999694824219</v>
+      </c>
+      <c r="F42" t="n">
+        <v>74.01141470009249</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-22.05222003278573</v>
+      </c>
+      <c r="H42" t="n">
+        <v>95</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9311530322265625</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.5331379196872597</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:38:27</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>15384600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2484,496 @@
         <v>15384600</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E43" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="F43" t="n">
+        <v>422.4441942321271</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.761882941473363</v>
+      </c>
+      <c r="H43" t="n">
+        <v>420</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5437667694091797</v>
+      </c>
+      <c r="J43" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.5121356650507439</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>60856884</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E44" t="n">
+        <v>246.6999969482422</v>
+      </c>
+      <c r="F44" t="n">
+        <v>244.634780128248</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.8371369459025468</v>
+      </c>
+      <c r="H44" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.3999083447265626</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.4966574651493966</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>77073685</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E45" t="n">
+        <v>454.5199890136719</v>
+      </c>
+      <c r="F45" t="n">
+        <v>439.2346291990858</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-3.36296756667533</v>
+      </c>
+      <c r="H45" t="n">
+        <v>455</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4267635449218751</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.5114856572073657</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>25927390</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E46" t="n">
+        <v>231</v>
+      </c>
+      <c r="F46" t="n">
+        <v>219.5560130731671</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-4.95410689473286</v>
+      </c>
+      <c r="H46" t="n">
+        <v>230</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.3436344934082031</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.5481897955312616</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>44670417</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>322</v>
+      </c>
+      <c r="F47" t="n">
+        <v>324.2653061768796</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.7035112350557824</v>
+      </c>
+      <c r="H47" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.3202582623291015</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.5035907212025394</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>34767598</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E48" t="n">
+        <v>604.1199951171875</v>
+      </c>
+      <c r="F48" t="n">
+        <v>591.2715743242152</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-2.126799459845718</v>
+      </c>
+      <c r="H48" t="n">
+        <v>605</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.5455978057861328</v>
+      </c>
+      <c r="J48" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.5137531537877139</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>14984947</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E49" t="n">
+        <v>178.0700073242188</v>
+      </c>
+      <c r="F49" t="n">
+        <v>177.9912983268548</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.04420115355004076</v>
+      </c>
+      <c r="H49" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.4476373596191406</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.5363657065021067</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>217924041</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E50" t="n">
+        <v>302.739990234375</v>
+      </c>
+      <c r="F50" t="n">
+        <v>291.899392513997</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-3.580827796151209</v>
+      </c>
+      <c r="H50" t="n">
+        <v>305</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2688671746826171</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.4453054824528134</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>10599210</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E51" t="n">
+        <v>19</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19.38768473316684</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.040445964036016</v>
+      </c>
+      <c r="H51" t="n">
+        <v>19</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9775392871093751</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.5325053415931197</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>25351780</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E52" t="n">
+        <v>89.93000030517578</v>
+      </c>
+      <c r="F52" t="n">
+        <v>94.42522463417122</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.998581467520265</v>
+      </c>
+      <c r="H52" t="n">
+        <v>90</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9777834252929689</v>
+      </c>
+      <c r="J52" t="n">
+        <v>6</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.5304971014851161</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-01-20 21:42:16</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>11795650</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2974,6 +2974,496 @@
         <v>11795650</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E53" t="n">
+        <v>449.0599975585938</v>
+      </c>
+      <c r="F53" t="n">
+        <v>449.9395284454999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.1958604399607947</v>
+      </c>
+      <c r="H53" t="n">
+        <v>450</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5053150054931641</v>
+      </c>
+      <c r="J53" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.5134632955567349</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>56636400</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E54" t="n">
+        <v>248.0399932861328</v>
+      </c>
+      <c r="F54" t="n">
+        <v>232.5727662347361</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-6.235779499297965</v>
+      </c>
+      <c r="H54" t="n">
+        <v>250</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.3436344934082031</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.4683809791720057</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>41625700</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E55" t="n">
+        <v>465.9500122070312</v>
+      </c>
+      <c r="F55" t="n">
+        <v>437.2762474185981</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-6.153828530364503</v>
+      </c>
+      <c r="H55" t="n">
+        <v>465</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.4061949029541015</v>
+      </c>
+      <c r="J55" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.5310574122964966</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>37962400</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E56" t="n">
+        <v>239.1600036621094</v>
+      </c>
+      <c r="F56" t="n">
+        <v>238.4460134346778</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.298540816398533</v>
+      </c>
+      <c r="H56" t="n">
+        <v>240</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.5017139672851563</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5070951647253836</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>33744100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E57" t="n">
+        <v>327.9299926757812</v>
+      </c>
+      <c r="F57" t="n">
+        <v>316.8634796522791</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-3.374657173991217</v>
+      </c>
+      <c r="H57" t="n">
+        <v>330</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4477594287109374</v>
+      </c>
+      <c r="J57" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.4901217168412471</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>27252600</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E58" t="n">
+        <v>658.760009765625</v>
+      </c>
+      <c r="F58" t="n">
+        <v>669.0186022269005</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.557257925374875</v>
+      </c>
+      <c r="H58" t="n">
+        <v>660</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5012562081909181</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.5142012437861804</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>22773600</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E59" t="n">
+        <v>187.6699981689453</v>
+      </c>
+      <c r="F59" t="n">
+        <v>187.7827465532708</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.06007800150561558</v>
+      </c>
+      <c r="H59" t="n">
+        <v>190</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.3787903918457031</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.4479065315528447</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>142524700</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E60" t="n">
+        <v>297.7200012207031</v>
+      </c>
+      <c r="F60" t="n">
+        <v>278.675921023481</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-6.396641179342394</v>
+      </c>
+      <c r="H60" t="n">
+        <v>300</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2362136926269531</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.4468279746449129</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>11100600</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E61" t="n">
+        <v>19.77000045776367</v>
+      </c>
+      <c r="F61" t="n">
+        <v>20.3810511182384</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.090797401751056</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.00391123046875</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.5131187702440942</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>24046500</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E62" t="n">
+        <v>87.62999725341797</v>
+      </c>
+      <c r="F62" t="n">
+        <v>69.58352394009626</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-20.59394485786979</v>
+      </c>
+      <c r="H62" t="n">
+        <v>88</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8693860717773438</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.523263581215079</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-01-24 21:37:57</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>9330600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3464,6 +3464,496 @@
         <v>9330600</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E63" t="n">
+        <v>430.8999938964844</v>
+      </c>
+      <c r="F63" t="n">
+        <v>435.0557319915666</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.9644321545477992</v>
+      </c>
+      <c r="H63" t="n">
+        <v>430</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5367477966308594</v>
+      </c>
+      <c r="J63" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.5301812370693845</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>36827538</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E64" t="n">
+        <v>258.2699890136719</v>
+      </c>
+      <c r="F64" t="n">
+        <v>258.1370017680728</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.05149155970733825</v>
+      </c>
+      <c r="H64" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.3531558825683593</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.5378061584161717</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>42113358</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E65" t="n">
+        <v>480.5799865722656</v>
+      </c>
+      <c r="F65" t="n">
+        <v>465.406381101719</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-3.157352760103944</v>
+      </c>
+      <c r="H65" t="n">
+        <v>480</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.4392756268310547</v>
+      </c>
+      <c r="J65" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.5250051800761603</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>29078464</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E66" t="n">
+        <v>244.6799926757812</v>
+      </c>
+      <c r="F66" t="n">
+        <v>244.8156377426456</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.05543774355268483</v>
+      </c>
+      <c r="H66" t="n">
+        <v>245</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.5772747351074219</v>
+      </c>
+      <c r="J66" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.5155810539106583</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>37754354</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E67" t="n">
+        <v>334.5499877929688</v>
+      </c>
+      <c r="F67" t="n">
+        <v>325.0138007234626</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-2.850452075164179</v>
+      </c>
+      <c r="H67" t="n">
+        <v>335</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.4906667144775391</v>
+      </c>
+      <c r="J67" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.5122369454953912</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>19709067</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E68" t="n">
+        <v>672.969970703125</v>
+      </c>
+      <c r="F68" t="n">
+        <v>676.0857782993397</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.4629935557093727</v>
+      </c>
+      <c r="H68" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.5655255850219728</v>
+      </c>
+      <c r="J68" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.5241604161023187</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>13139173</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E69" t="n">
+        <v>188.5200042724609</v>
+      </c>
+      <c r="F69" t="n">
+        <v>188.7212843992421</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.1067685774556909</v>
+      </c>
+      <c r="H69" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.397466962890625</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.5517104411470134</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>138307845</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E70" t="n">
+        <v>300.3099975585938</v>
+      </c>
+      <c r="F70" t="n">
+        <v>280.4698287761678</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-6.606562866277828</v>
+      </c>
+      <c r="H70" t="n">
+        <v>300</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.232978861694336</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.5266066962026991</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>9686247</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E71" t="n">
+        <v>19.20000076293945</v>
+      </c>
+      <c r="F71" t="n">
+        <v>19.16654049277127</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.1742722335343196</v>
+      </c>
+      <c r="H71" t="n">
+        <v>19</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.9707034179687499</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.5595245498130642</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:13</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>22918607</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E72" t="n">
+        <v>85.26999664306641</v>
+      </c>
+      <c r="F72" t="n">
+        <v>80.22426737745849</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-5.917356003576439</v>
+      </c>
+      <c r="H72" t="n">
+        <v>85</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.9150399121093751</v>
+      </c>
+      <c r="J72" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.5394558642722411</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:41:14</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>8937891</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3954,6 +3954,496 @@
         <v>8937891</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E73" t="n">
+        <v>431.4599914550781</v>
+      </c>
+      <c r="F73" t="n">
+        <v>435.5712527834045</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.9528719718510442</v>
+      </c>
+      <c r="H73" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.5361374511718751</v>
+      </c>
+      <c r="J73" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.5070365387711249</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:16</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>45585387</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E74" t="n">
+        <v>256.4400024414062</v>
+      </c>
+      <c r="F74" t="n">
+        <v>255.0595757556952</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.538303959042622</v>
+      </c>
+      <c r="H74" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.3781800463867187</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.4864634187979441</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:16</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>33041915</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E75" t="n">
+        <v>481.6300048828125</v>
+      </c>
+      <c r="F75" t="n">
+        <v>467.2470727305305</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2.986303180131312</v>
+      </c>
+      <c r="H75" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4722953161621094</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.5074015771674634</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:16</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>29736039</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E76" t="n">
+        <v>243.0099945068359</v>
+      </c>
+      <c r="F76" t="n">
+        <v>242.6760973427143</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.1374005891400497</v>
+      </c>
+      <c r="H76" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.5892375061035158</v>
+      </c>
+      <c r="J76" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.529987221352478</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:16</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>37958492</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E77" t="n">
+        <v>336.010009765625</v>
+      </c>
+      <c r="F77" t="n">
+        <v>324.6799555466426</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-3.371939492780407</v>
+      </c>
+      <c r="H77" t="n">
+        <v>335</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.4982960327148438</v>
+      </c>
+      <c r="J77" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.5345077659957792</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:16</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>26310723</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E78" t="n">
+        <v>668.72998046875</v>
+      </c>
+      <c r="F78" t="n">
+        <v>669.803518149319</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1605338046630508</v>
+      </c>
+      <c r="H78" t="n">
+        <v>667.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5896647479248047</v>
+      </c>
+      <c r="J78" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.528806244567088</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:16</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>16982940</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E79" t="n">
+        <v>191.5200042724609</v>
+      </c>
+      <c r="F79" t="n">
+        <v>191.3256144984148</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-0.1014984177681962</v>
+      </c>
+      <c r="H79" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.4002745520019532</v>
+      </c>
+      <c r="J79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.4818932284985512</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:17</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>141003489</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E80" t="n">
+        <v>300.7699890136719</v>
+      </c>
+      <c r="F80" t="n">
+        <v>280.7585933419596</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-6.653388437236206</v>
+      </c>
+      <c r="H80" t="n">
+        <v>300</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.2270585107421875</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.5448354913503161</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:17</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>7436194</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E81" t="n">
+        <v>20.47999954223633</v>
+      </c>
+      <c r="F81" t="n">
+        <v>21.27979629954244</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.905257691323078</v>
+      </c>
+      <c r="H81" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.001958115234375</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.5287072522138597</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:17</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>29074059</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E82" t="n">
+        <v>94.38999938964844</v>
+      </c>
+      <c r="F82" t="n">
+        <v>92.12140312790468</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-2.403428622113695</v>
+      </c>
+      <c r="H82" t="n">
+        <v>94</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.9741213525390625</v>
+      </c>
+      <c r="J82" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.5419614889915186</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-01-28 21:52:17</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>14568700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4444,6 +4444,496 @@
         <v>14568700</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E83" t="n">
+        <v>430.4100036621094</v>
+      </c>
+      <c r="F83" t="n">
+        <v>425.7584343434405</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-1.080729834132899</v>
+      </c>
+      <c r="H83" t="n">
+        <v>430</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.288947540283203</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.525091986090393</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>82001826</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E84" t="n">
+        <v>259.4800109863281</v>
+      </c>
+      <c r="F84" t="n">
+        <v>257.9339215458453</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-0.5958414425087617</v>
+      </c>
+      <c r="H84" t="n">
+        <v>260</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.1853108813476562</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.4494299911238307</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>79605051</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E85" t="n">
+        <v>430.2900085449219</v>
+      </c>
+      <c r="F85" t="n">
+        <v>429.6407892359655</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-0.1508794757172604</v>
+      </c>
+      <c r="H85" t="n">
+        <v>430</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.1782308740234375</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.5279664736987753</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>57685975</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E86" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="F86" t="n">
+        <v>237.7940321814411</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-0.6293233811580643</v>
+      </c>
+      <c r="H86" t="n">
+        <v>240</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.2019122778320313</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.4297710927033775</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>42577859</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E87" t="n">
+        <v>338</v>
+      </c>
+      <c r="F87" t="n">
+        <v>338.2283706662907</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.06756528588481851</v>
+      </c>
+      <c r="H87" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2157060852050781</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.5441887870583182</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>30131351</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E88" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>720.294375551144</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.5295709073473772</v>
+      </c>
+      <c r="H88" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.1915364050292969</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.4682433356267729</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>23473277</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E89" t="n">
+        <v>191.1300048828125</v>
+      </c>
+      <c r="F89" t="n">
+        <v>186.8489818881882</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-2.239848733980355</v>
+      </c>
+      <c r="H89" t="n">
+        <v>190</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.2544019873046875</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.6304434485552582</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>175685267</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E90" t="n">
+        <v>305.8900146484375</v>
+      </c>
+      <c r="F90" t="n">
+        <v>285.0314961766541</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-6.818960238292298</v>
+      </c>
+      <c r="H90" t="n">
+        <v>305</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.229499892578125</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.551914139990977</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:25</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>11927641</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E91" t="n">
+        <v>17.47999954223633</v>
+      </c>
+      <c r="F91" t="n">
+        <v>18.27152854716512</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4.528198087283981</v>
+      </c>
+      <c r="H91" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.9589847851562499</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.5224036051136834</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:26</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>25389107</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E92" t="n">
+        <v>79.62000274658203</v>
+      </c>
+      <c r="F92" t="n">
+        <v>80.74892459462478</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.417887225696201</v>
+      </c>
+      <c r="H92" t="n">
+        <v>80</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.9155281884765626</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.5089075721623851</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-01-30 21:47:26</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>10632755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4934,6 +4934,496 @@
         <v>10632755</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E93" t="n">
+        <v>430.4100036621094</v>
+      </c>
+      <c r="F93" t="n">
+        <v>429.6151217483585</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-0.1846801670471632</v>
+      </c>
+      <c r="H93" t="n">
+        <v>430</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.4054014538574219</v>
+      </c>
+      <c r="J93" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.5203437262491839</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:16</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>82483000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E94" t="n">
+        <v>259.4800109863281</v>
+      </c>
+      <c r="F94" t="n">
+        <v>259.8750216026365</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.1522316169198742</v>
+      </c>
+      <c r="H94" t="n">
+        <v>260</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.25586681640625</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.4744551874549628</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:16</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>92352600</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E95" t="n">
+        <v>430.2900085449219</v>
+      </c>
+      <c r="F95" t="n">
+        <v>432.3509430541635</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.4789640633792392</v>
+      </c>
+      <c r="H95" t="n">
+        <v>430</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.2565992309570312</v>
+      </c>
+      <c r="J95" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.5204220406205725</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:16</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>58470400</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E96" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="F96" t="n">
+        <v>233.3015404227033</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-2.506670519246535</v>
+      </c>
+      <c r="H96" t="n">
+        <v>240</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.2946847875976562</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.465437322579172</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:16</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>46535400</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E97" t="n">
+        <v>338</v>
+      </c>
+      <c r="F97" t="n">
+        <v>333.0593929412761</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-1.4617180647112</v>
+      </c>
+      <c r="H97" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.5667767932128907</v>
+      </c>
+      <c r="J97" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.5245910042813593</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:16</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>30980500</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E98" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>703.8337944452578</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-1.767788632901911</v>
+      </c>
+      <c r="H98" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.287970987548828</v>
+      </c>
+      <c r="J98" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.487665319424866</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:17</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>23702600</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E99" t="n">
+        <v>191.1300048828125</v>
+      </c>
+      <c r="F99" t="n">
+        <v>189.2059735295701</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-1.006661070522193</v>
+      </c>
+      <c r="H99" t="n">
+        <v>190</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.3940490283203125</v>
+      </c>
+      <c r="J99" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.5756397816567489</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:17</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>178936900</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E100" t="n">
+        <v>305.8900146484375</v>
+      </c>
+      <c r="F100" t="n">
+        <v>303.3763241158534</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-0.8217628599197899</v>
+      </c>
+      <c r="H100" t="n">
+        <v>305</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.2469557727050781</v>
+      </c>
+      <c r="J100" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.5435924808142418</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:17</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>11951400</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E101" t="n">
+        <v>17.47999954223633</v>
+      </c>
+      <c r="F101" t="n">
+        <v>18.59736006391511</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6.39222283146486</v>
+      </c>
+      <c r="H101" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1.033207958984375</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.5369810897019615</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:17</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>25594700</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E102" t="n">
+        <v>79.62000274658203</v>
+      </c>
+      <c r="F102" t="n">
+        <v>83.17402605553951</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4.463731708562459</v>
+      </c>
+      <c r="H102" t="n">
+        <v>80</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.9697268652343749</v>
+      </c>
+      <c r="J102" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.5264884933011161</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-01-31 21:43:17</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>10707200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5424,6 +5424,496 @@
         <v>10707200</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E103" t="n">
+        <v>430.4100036621094</v>
+      </c>
+      <c r="F103" t="n">
+        <v>429.5682021212657</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-0.1955813140218104</v>
+      </c>
+      <c r="H103" t="n">
+        <v>430</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.4532525378417969</v>
+      </c>
+      <c r="J103" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.5199709498559087</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:27</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>82483000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E104" t="n">
+        <v>259.4800109863281</v>
+      </c>
+      <c r="F104" t="n">
+        <v>259.8603722016688</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.1465859408186541</v>
+      </c>
+      <c r="H104" t="n">
+        <v>260</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.286139951171875</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.4696438076487838</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>92352600</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E105" t="n">
+        <v>430.2900085449219</v>
+      </c>
+      <c r="F105" t="n">
+        <v>432.3455875944375</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.4777194470461525</v>
+      </c>
+      <c r="H105" t="n">
+        <v>430</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.2868723657226562</v>
+      </c>
+      <c r="J105" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.5199819663635014</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>58470400</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E106" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="F106" t="n">
+        <v>232.9674621499871</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-2.646276983289913</v>
+      </c>
+      <c r="H106" t="n">
+        <v>240</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.3295965478515624</v>
+      </c>
+      <c r="J106" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.4598610613408551</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>46535400</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E107" t="n">
+        <v>338</v>
+      </c>
+      <c r="F107" t="n">
+        <v>336.040497165381</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-0.5797345664553261</v>
+      </c>
+      <c r="H107" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.6051064880371095</v>
+      </c>
+      <c r="J107" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.5240148979677688</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>30980500</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E108" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>704.0144317539018</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-1.742577564005329</v>
+      </c>
+      <c r="H108" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.3219672296142577</v>
+      </c>
+      <c r="J108" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.4841638853542514</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>23702600</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E109" t="n">
+        <v>191.1300048828125</v>
+      </c>
+      <c r="F109" t="n">
+        <v>189.1972916728533</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-1.01120345345262</v>
+      </c>
+      <c r="H109" t="n">
+        <v>190</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.4406794213867187</v>
+      </c>
+      <c r="J109" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.5804832740994962</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>178936900</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E110" t="n">
+        <v>305.8900146484375</v>
+      </c>
+      <c r="F110" t="n">
+        <v>303.4935207492527</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-0.7834495355917777</v>
+      </c>
+      <c r="H110" t="n">
+        <v>305</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.256294058227539</v>
+      </c>
+      <c r="J110" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.5430247220984498</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>11951400</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E111" t="n">
+        <v>17.47999954223633</v>
+      </c>
+      <c r="F111" t="n">
+        <v>18.59698525062723</v>
+      </c>
+      <c r="G111" t="n">
+        <v>6.390078590631338</v>
+      </c>
+      <c r="H111" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.072270263671875</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.5365663106650599</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>25594700</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E112" t="n">
+        <v>79.62000274658203</v>
+      </c>
+      <c r="F112" t="n">
+        <v>83.17257377262925</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4.46190769090337</v>
+      </c>
+      <c r="H112" t="n">
+        <v>80</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.006352624511718</v>
+      </c>
+      <c r="J112" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.5260216696843615</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-02-01 21:44:28</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>10707200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +465,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>percent increase %</t>
+          <t>percent change %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -492,6 +496,56 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>current_volume</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_std</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>expected_std_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>p25</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>p50</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>p75</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>realized_price</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>landed_in_50_pct_interval</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pdf_directional_correct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>z_score</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>abs_error_pct</t>
         </is>
       </c>
     </row>
@@ -506,10 +560,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C2" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D2" t="n">
         <v>1.86</v>
@@ -541,6 +593,22 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>41.70415319067947</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -553,10 +621,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C3" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D3" t="n">
         <v>1.86</v>
@@ -588,6 +654,22 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>255.5299987792969</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>5.687886901634231</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,10 +682,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D4" t="n">
         <v>1.86</v>
@@ -635,6 +715,22 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>459.8599853515625</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>2.362199978186848</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,10 +743,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C5" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D5" t="n">
         <v>1.86</v>
@@ -682,6 +776,22 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>239.1199951171875</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>7.770265471297484</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -694,10 +804,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D6" t="n">
         <v>1.86</v>
@@ -729,6 +837,22 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>330</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>5.138559158441261</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -741,10 +865,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C7" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D7" t="n">
         <v>1.86</v>
@@ -776,6 +898,22 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>620.25</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>18.78678604480787</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -788,10 +926,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C8" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D8" t="n">
         <v>1.86</v>
@@ -823,6 +959,22 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>186.2299957275391</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>54.85904986641415</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -835,10 +987,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C9" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D9" t="n">
         <v>1.86</v>
@@ -870,6 +1020,22 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>312.4700012207031</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>3.769465294549332</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -882,10 +1048,8 @@
           <t>V</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D10" t="n">
         <v>1.86</v>
@@ -917,6 +1081,22 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>328.2999877929688</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>5.054832113308425</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -929,10 +1109,8 @@
           <t>UNH</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C11" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D11" t="n">
         <v>1.86</v>
@@ -964,6 +1142,22 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>331.0199890136719</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>1.995285840329405</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -976,10 +1170,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C12" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D12" t="n">
         <v>1.71</v>
@@ -1013,6 +1205,22 @@
       <c r="M12" t="n">
         <v>85263000</v>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>0.7383414087756618</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1025,10 +1233,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C13" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D13" t="n">
         <v>1.14</v>
@@ -1062,6 +1268,22 @@
       <c r="M13" t="n">
         <v>88816200</v>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>1.685545443082439</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1074,10 +1296,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C14" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D14" t="n">
         <v>1.14</v>
@@ -1111,6 +1331,22 @@
       <c r="M14" t="n">
         <v>52282100</v>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>255.5299987792969</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>3.475420656066156</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1123,10 +1359,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C15" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D15" t="n">
         <v>1.14</v>
@@ -1160,6 +1394,22 @@
       <c r="M15" t="n">
         <v>23007300</v>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>459.8599853515625</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>1.442328417867651</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1172,10 +1422,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D16" t="n">
         <v>1.14</v>
@@ -1209,6 +1457,22 @@
       <c r="M16" t="n">
         <v>53667800</v>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>239.1199951171875</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>1.270212857742697</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1221,10 +1485,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C17" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D17" t="n">
         <v>1.14</v>
@@ -1258,6 +1520,22 @@
       <c r="M17" t="n">
         <v>31178900</v>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>330</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>4.710270641162557</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1270,10 +1548,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C18" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D18" t="n">
         <v>1.14</v>
@@ -1307,6 +1583,22 @@
       <c r="M18" t="n">
         <v>11054900</v>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>620.25</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>6.012284741399252</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1319,10 +1611,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C19" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D19" t="n">
         <v>1.14</v>
@@ -1356,6 +1646,22 @@
       <c r="M19" t="n">
         <v>176174700</v>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>186.2299957275391</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>46.82076299672275</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1368,10 +1674,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C20" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D20" t="n">
         <v>1.14</v>
@@ -1405,6 +1709,22 @@
       <c r="M20" t="n">
         <v>7657900</v>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>312.4700012207031</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>6.95112716311954</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1417,10 +1737,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C21" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D21" t="n">
         <v>1.14</v>
@@ -1454,6 +1772,22 @@
       <c r="M21" t="n">
         <v>51253400</v>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>20.19000053405762</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>5.659997100139047</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1466,10 +1800,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="C22" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="D22" t="n">
         <v>1.14</v>
@@ -1503,6 +1835,22 @@
       <c r="M22" t="n">
         <v>20066600</v>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>94.94999694824219</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>1.58240778421954</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1515,10 +1863,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C23" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D23" t="n">
         <v>1.57</v>
@@ -1552,6 +1898,22 @@
       <c r="M23" t="n">
         <v>67185700</v>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>449.0599975585938</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>2.118221959355954</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1564,10 +1926,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C24" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D24" t="n">
         <v>1.57</v>
@@ -1601,6 +1961,22 @@
       <c r="M24" t="n">
         <v>39952300</v>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>248.0399932861328</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>0.5887346077448081</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1613,10 +1989,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C25" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D25" t="n">
         <v>1.57</v>
@@ -1650,6 +2024,22 @@
       <c r="M25" t="n">
         <v>18484000</v>
       </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>465.9500122070312</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>2.369069560526695</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1662,10 +2052,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C26" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D26" t="n">
         <v>1.57</v>
@@ -1699,6 +2087,22 @@
       <c r="M26" t="n">
         <v>34534700</v>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>239.1600036621094</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>3.777522711619161</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1711,10 +2115,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C27" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D27" t="n">
         <v>1.57</v>
@@ -1748,6 +2150,22 @@
       <c r="M27" t="n">
         <v>26183500</v>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>327.9299926757812</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>0.07897825318008098</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1760,10 +2178,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C28" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D28" t="n">
         <v>1.57</v>
@@ -1797,6 +2213,22 @@
       <c r="M28" t="n">
         <v>11621500</v>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>658.760009765625</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>4.247778629828026</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1809,10 +2241,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C29" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D29" t="n">
         <v>1.57</v>
@@ -1846,6 +2276,22 @@
       <c r="M29" t="n">
         <v>131072000</v>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>187.6699981689453</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>1.875463000401539</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1858,10 +2304,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C30" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D30" t="n">
         <v>1.57</v>
@@ -1895,6 +2339,22 @@
       <c r="M30" t="n">
         <v>6735300</v>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>297.7200012207031</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>8.234952088584151</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1907,10 +2367,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C31" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D31" t="n">
         <v>1.57</v>
@@ -1944,6 +2402,22 @@
       <c r="M31" t="n">
         <v>51227900</v>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>19.77000045776367</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>0.878424992619266</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1956,10 +2430,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="C32" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="D32" t="n">
         <v>1.57</v>
@@ -1993,6 +2465,22 @@
       <c r="M32" t="n">
         <v>33864400</v>
       </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>87.62999725341797</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>15.96645475614419</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2005,10 +2493,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C33" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D33" t="n">
         <v>1.57</v>
@@ -2042,6 +2528,22 @@
       <c r="M33" t="n">
         <v>60047300</v>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>430.4100036621094</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="n">
+        <v>1.915810253901145</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2054,10 +2556,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C34" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D34" t="n">
         <v>1.57</v>
@@ -2091,6 +2591,22 @@
       <c r="M34" t="n">
         <v>72018600</v>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>259.4800109863281</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="n">
+        <v>3.14124009980618</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2103,10 +2619,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C35" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D35" t="n">
         <v>1.57</v>
@@ -2140,6 +2654,22 @@
       <c r="M35" t="n">
         <v>33795700</v>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>430.2900085449219</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="n">
+        <v>1.122746641238114</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2152,10 +2682,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C36" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D36" t="n">
         <v>1.57</v>
@@ -2189,6 +2717,22 @@
       <c r="M36" t="n">
         <v>45824700</v>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>3.70699035708306</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2201,10 +2745,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C37" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D37" t="n">
         <v>1.57</v>
@@ -2238,6 +2780,22 @@
       <c r="M37" t="n">
         <v>40250800</v>
       </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>338</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>2.187819571493209</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2250,10 +2808,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C38" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D38" t="n">
         <v>1.57</v>
@@ -2287,6 +2843,22 @@
       <c r="M38" t="n">
         <v>16869800</v>
       </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>15.85514480513487</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2299,10 +2871,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C39" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D39" t="n">
         <v>1.57</v>
@@ -2336,6 +2906,22 @@
       <c r="M39" t="n">
         <v>187613900</v>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>191.1300048828125</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>2.697635967764349</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2348,10 +2934,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C40" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D40" t="n">
         <v>1.57</v>
@@ -2385,6 +2969,22 @@
       <c r="M40" t="n">
         <v>14637600</v>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>305.8900146484375</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="n">
+        <v>5.341546033803081</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2397,10 +2997,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C41" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D41" t="n">
         <v>1.57</v>
@@ -2434,6 +3032,22 @@
       <c r="M41" t="n">
         <v>34785200</v>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>17.47999954223633</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>15.10621306664131</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2446,10 +3060,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C42" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D42" t="n">
         <v>1.57</v>
@@ -2483,6 +3095,22 @@
       <c r="M42" t="n">
         <v>15384600</v>
       </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>79.62000274658203</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>5.906885968144706</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2495,10 +3123,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C43" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D43" t="n">
         <v>1.29</v>
@@ -2532,6 +3158,22 @@
       <c r="M43" t="n">
         <v>60856884</v>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>430.4100036621094</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>1.900014175308838</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2544,10 +3186,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C44" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D44" t="n">
         <v>1.29</v>
@@ -2581,6 +3221,22 @@
       <c r="M44" t="n">
         <v>77073685</v>
       </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>259.4800109863281</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>6.017523729923137</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2593,10 +3249,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C45" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D45" t="n">
         <v>1.29</v>
@@ -2630,6 +3284,22 @@
       <c r="M45" t="n">
         <v>25927390</v>
       </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>430.2900085449219</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>1.967926795381245</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2642,10 +3312,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C46" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D46" t="n">
         <v>1.29</v>
@@ -2679,6 +3347,22 @@
       <c r="M46" t="n">
         <v>44670417</v>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>239.3000030517578</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>8.547181808913731</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2691,10 +3375,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C47" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D47" t="n">
         <v>1.29</v>
@@ -2728,6 +3410,22 @@
       <c r="M47" t="n">
         <v>34767598</v>
       </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>338</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>4.2654328643231</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2740,10 +3438,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C48" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D48" t="n">
         <v>1.29</v>
@@ -2777,6 +3473,22 @@
       <c r="M48" t="n">
         <v>14984947</v>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>20.72906486922237</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2789,10 +3501,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C49" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D49" t="n">
         <v>1.29</v>
@@ -2826,6 +3536,22 @@
       <c r="M49" t="n">
         <v>217924041</v>
       </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>191.1300048828125</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>7.37839389877463</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2838,10 +3564,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C50" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D50" t="n">
         <v>1.29</v>
@@ -2875,6 +3599,22 @@
       <c r="M50" t="n">
         <v>10599210</v>
       </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>305.8900146484375</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="n">
+        <v>4.621332690012068</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2887,10 +3627,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C51" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D51" t="n">
         <v>1.29</v>
@@ -2924,6 +3662,22 @@
       <c r="M51" t="n">
         <v>25351780</v>
       </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>17.47999954223633</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="n">
+        <v>10.04044837331848</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2936,10 +3690,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="C52" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="D52" t="n">
         <v>1.29</v>
@@ -2973,6 +3725,22 @@
       <c r="M52" t="n">
         <v>11795650</v>
       </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>79.62000274658203</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>16.46305108122755</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2985,10 +3753,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C53" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D53" t="n">
         <v>1.71</v>
@@ -3022,6 +3788,16 @@
       <c r="M53" t="n">
         <v>56636400</v>
       </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3034,10 +3810,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C54" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D54" t="n">
         <v>1.71</v>
@@ -3071,6 +3845,16 @@
       <c r="M54" t="n">
         <v>41625700</v>
       </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3083,10 +3867,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C55" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D55" t="n">
         <v>1.71</v>
@@ -3120,6 +3902,16 @@
       <c r="M55" t="n">
         <v>37962400</v>
       </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3132,10 +3924,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C56" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D56" t="n">
         <v>1.71</v>
@@ -3169,6 +3959,16 @@
       <c r="M56" t="n">
         <v>33744100</v>
       </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3181,10 +3981,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C57" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D57" t="n">
         <v>1.71</v>
@@ -3218,6 +4016,16 @@
       <c r="M57" t="n">
         <v>27252600</v>
       </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3230,10 +4038,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C58" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D58" t="n">
         <v>1.71</v>
@@ -3267,6 +4073,16 @@
       <c r="M58" t="n">
         <v>22773600</v>
       </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3279,10 +4095,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C59" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D59" t="n">
         <v>1.71</v>
@@ -3316,6 +4130,16 @@
       <c r="M59" t="n">
         <v>142524700</v>
       </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3328,10 +4152,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C60" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D60" t="n">
         <v>1.71</v>
@@ -3365,6 +4187,16 @@
       <c r="M60" t="n">
         <v>11100600</v>
       </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3377,10 +4209,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C61" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D61" t="n">
         <v>1.71</v>
@@ -3414,6 +4244,16 @@
       <c r="M61" t="n">
         <v>24046500</v>
       </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3426,10 +4266,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C62" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D62" t="n">
         <v>1.71</v>
@@ -3463,6 +4301,16 @@
       <c r="M62" t="n">
         <v>9330600</v>
       </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3475,10 +4323,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C63" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D63" t="n">
         <v>1.29</v>
@@ -3512,6 +4358,16 @@
       <c r="M63" t="n">
         <v>36827538</v>
       </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3524,10 +4380,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C64" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D64" t="n">
         <v>1.29</v>
@@ -3561,6 +4415,16 @@
       <c r="M64" t="n">
         <v>42113358</v>
       </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3573,10 +4437,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C65" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D65" t="n">
         <v>1.29</v>
@@ -3610,6 +4472,16 @@
       <c r="M65" t="n">
         <v>29078464</v>
       </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3622,10 +4494,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C66" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D66" t="n">
         <v>1.29</v>
@@ -3659,6 +4529,16 @@
       <c r="M66" t="n">
         <v>37754354</v>
       </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3671,10 +4551,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C67" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D67" t="n">
         <v>1.29</v>
@@ -3708,6 +4586,16 @@
       <c r="M67" t="n">
         <v>19709067</v>
       </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3720,10 +4608,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C68" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D68" t="n">
         <v>1.29</v>
@@ -3757,6 +4643,16 @@
       <c r="M68" t="n">
         <v>13139173</v>
       </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3769,10 +4665,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C69" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D69" t="n">
         <v>1.29</v>
@@ -3806,6 +4700,16 @@
       <c r="M69" t="n">
         <v>138307845</v>
       </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3818,10 +4722,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C70" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D70" t="n">
         <v>1.29</v>
@@ -3855,6 +4757,16 @@
       <c r="M70" t="n">
         <v>9686247</v>
       </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3867,10 +4779,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C71" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D71" t="n">
         <v>1.29</v>
@@ -3904,6 +4814,16 @@
       <c r="M71" t="n">
         <v>22918607</v>
       </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3916,10 +4836,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C72" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D72" t="n">
         <v>1.29</v>
@@ -3953,6 +4871,16 @@
       <c r="M72" t="n">
         <v>8937891</v>
       </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3965,10 +4893,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C73" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D73" t="n">
         <v>1.14</v>
@@ -4002,6 +4928,16 @@
       <c r="M73" t="n">
         <v>45585387</v>
       </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4014,10 +4950,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C74" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D74" t="n">
         <v>1.14</v>
@@ -4051,6 +4985,16 @@
       <c r="M74" t="n">
         <v>33041915</v>
       </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4063,10 +5007,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C75" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D75" t="n">
         <v>1.14</v>
@@ -4100,6 +5042,16 @@
       <c r="M75" t="n">
         <v>29736039</v>
       </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4112,10 +5064,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C76" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D76" t="n">
         <v>1.14</v>
@@ -4149,6 +5099,16 @@
       <c r="M76" t="n">
         <v>37958492</v>
       </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4161,10 +5121,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C77" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D77" t="n">
         <v>1.14</v>
@@ -4198,6 +5156,16 @@
       <c r="M77" t="n">
         <v>26310723</v>
       </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4210,10 +5178,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C78" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D78" t="n">
         <v>1.14</v>
@@ -4247,6 +5213,16 @@
       <c r="M78" t="n">
         <v>16982940</v>
       </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4259,10 +5235,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C79" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D79" t="n">
         <v>1.14</v>
@@ -4296,6 +5270,16 @@
       <c r="M79" t="n">
         <v>141003489</v>
       </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4308,10 +5292,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C80" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D80" t="n">
         <v>1.14</v>
@@ -4345,6 +5327,16 @@
       <c r="M80" t="n">
         <v>7436194</v>
       </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4357,10 +5349,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C81" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D81" t="n">
         <v>1.14</v>
@@ -4394,6 +5384,16 @@
       <c r="M81" t="n">
         <v>29074059</v>
       </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4406,10 +5406,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C82" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D82" t="n">
         <v>1.14</v>
@@ -4443,6 +5441,16 @@
       <c r="M82" t="n">
         <v>14568700</v>
       </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4455,10 +5463,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C83" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D83" t="n">
         <v>0.29</v>
@@ -4492,6 +5498,16 @@
       <c r="M83" t="n">
         <v>82001826</v>
       </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4504,10 +5520,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C84" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D84" t="n">
         <v>0.29</v>
@@ -4541,6 +5555,16 @@
       <c r="M84" t="n">
         <v>79605051</v>
       </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4553,10 +5577,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C85" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D85" t="n">
         <v>0.29</v>
@@ -4590,6 +5612,16 @@
       <c r="M85" t="n">
         <v>57685975</v>
       </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4602,10 +5634,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C86" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D86" t="n">
         <v>0.29</v>
@@ -4639,6 +5669,16 @@
       <c r="M86" t="n">
         <v>42577859</v>
       </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4651,10 +5691,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C87" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D87" t="n">
         <v>0.29</v>
@@ -4688,6 +5726,16 @@
       <c r="M87" t="n">
         <v>30131351</v>
       </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4700,10 +5748,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C88" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D88" t="n">
         <v>0.29</v>
@@ -4737,6 +5783,16 @@
       <c r="M88" t="n">
         <v>23473277</v>
       </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4749,10 +5805,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="C89" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="D89" t="n">
         <v>0.29</v>
@@ -4786,6 +5840,16 @@
       <c r="M89" t="n">
         <v>175685267</v>
       </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4798,10 +5862,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C90" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D90" t="n">
         <v>0.86</v>
@@ -4835,6 +5897,16 @@
       <c r="M90" t="n">
         <v>11927641</v>
       </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4847,10 +5919,8 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C91" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D91" t="n">
         <v>0.86</v>
@@ -4884,6 +5954,16 @@
       <c r="M91" t="n">
         <v>25389107</v>
       </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4896,10 +5976,8 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C92" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D92" t="n">
         <v>0.86</v>
@@ -4933,6 +6011,16 @@
       <c r="M92" t="n">
         <v>10632755</v>
       </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4945,10 +6033,8 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C93" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="D93" t="n">
         <v>0.43</v>
@@ -4957,31 +6043,51 @@
         <v>430.4100036621094</v>
       </c>
       <c r="F93" t="n">
-        <v>429.6151217483585</v>
+        <v>429.5748006068085</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.1846801670471632</v>
+        <v>-0.1940482442774646</v>
       </c>
       <c r="H93" t="n">
         <v>430</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4054014538574219</v>
+        <v>0.4532525378417969</v>
       </c>
       <c r="J93" t="n">
         <v>8.15</v>
       </c>
       <c r="K93" t="n">
-        <v>0.5203437262491839</v>
+        <v>0.5198350198646432</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:16</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M93" t="n">
         <v>82483000</v>
       </c>
+      <c r="N93" t="n">
+        <v>22.94365996162667</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.05330652114591287</v>
+      </c>
+      <c r="P93" t="n">
+        <v>416.4320866141732</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>431.5419947506562</v>
+      </c>
+      <c r="R93" t="n">
+        <v>444.750656167979</v>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4994,10 +6100,8 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C94" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="D94" t="n">
         <v>0.43</v>
@@ -5006,31 +6110,51 @@
         <v>259.4800109863281</v>
       </c>
       <c r="F94" t="n">
-        <v>259.8750216026365</v>
+        <v>259.862459834961</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1522316169198742</v>
+        <v>0.1473904857561505</v>
       </c>
       <c r="H94" t="n">
         <v>260</v>
       </c>
       <c r="I94" t="n">
-        <v>0.25586681640625</v>
+        <v>0.286139951171875</v>
       </c>
       <c r="J94" t="n">
         <v>2.8</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4744551874549628</v>
+        <v>0.4781900285089786</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:16</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M94" t="n">
         <v>92352600</v>
       </c>
+      <c r="N94" t="n">
+        <v>8.058732986203077</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.03105724003776032</v>
+      </c>
+      <c r="P94" t="n">
+        <v>254.9211165048544</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>260.127427184466</v>
+      </c>
+      <c r="R94" t="n">
+        <v>265.0333737864078</v>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5043,10 +6167,8 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C95" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="D95" t="n">
         <v>0.43</v>
@@ -5055,31 +6177,51 @@
         <v>430.2900085449219</v>
       </c>
       <c r="F95" t="n">
-        <v>432.3509430541635</v>
+        <v>432.3463565613438</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4789640633792392</v>
+        <v>0.4778981560310216</v>
       </c>
       <c r="H95" t="n">
         <v>430</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2565992309570312</v>
+        <v>0.2868723657226562</v>
       </c>
       <c r="J95" t="n">
         <v>5.2</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5204220406205725</v>
+        <v>0.5193045299093029</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:16</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M95" t="n">
         <v>58470400</v>
       </c>
+      <c r="N95" t="n">
+        <v>13.48014129421526</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.03132803696697491</v>
+      </c>
+      <c r="P95" t="n">
+        <v>423.8120830244625</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>431.317642698295</v>
+      </c>
+      <c r="R95" t="n">
+        <v>439.1234247590808</v>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5092,10 +6234,8 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C96" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="D96" t="n">
         <v>0.43</v>
@@ -5104,31 +6244,51 @@
         <v>239.3000030517578</v>
       </c>
       <c r="F96" t="n">
-        <v>233.3015404227033</v>
+        <v>232.9597662320612</v>
       </c>
       <c r="G96" t="n">
-        <v>-2.506670519246535</v>
+        <v>-2.649492995754476</v>
       </c>
       <c r="H96" t="n">
         <v>240</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2946847875976562</v>
+        <v>0.3295965478515624</v>
       </c>
       <c r="J96" t="n">
         <v>3.05</v>
       </c>
       <c r="K96" t="n">
-        <v>0.465437322579172</v>
+        <v>0.470282886150752</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:16</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M96" t="n">
         <v>46535400</v>
       </c>
+      <c r="N96" t="n">
+        <v>17.55984401824347</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.07338004092898184</v>
+      </c>
+      <c r="P96" t="n">
+        <v>227.1401334604385</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>237.4499523355577</v>
+      </c>
+      <c r="R96" t="n">
+        <v>244.556720686368</v>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5141,10 +6301,8 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C97" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D97" t="n">
         <v>0.71</v>
@@ -5153,31 +6311,51 @@
         <v>338</v>
       </c>
       <c r="F97" t="n">
-        <v>333.0593929412761</v>
+        <v>335.786033090697</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.4617180647112</v>
+        <v>-0.6550197956517742</v>
       </c>
       <c r="H97" t="n">
         <v>337.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5667767932128907</v>
+        <v>0.6121864953613283</v>
       </c>
       <c r="J97" t="n">
         <v>10.87</v>
       </c>
       <c r="K97" t="n">
-        <v>0.5245910042813593</v>
+        <v>0.5248070260002247</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:16</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M97" t="n">
         <v>30980500</v>
       </c>
+      <c r="N97" t="n">
+        <v>32.44723428384169</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.09599773456757899</v>
+      </c>
+      <c r="P97" t="n">
+        <v>319.5542295542296</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>336.960336960337</v>
+      </c>
+      <c r="R97" t="n">
+        <v>354.5665145665146</v>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5190,10 +6368,8 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C98" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="D98" t="n">
         <v>0.43</v>
@@ -5202,31 +6378,51 @@
         <v>716.5</v>
       </c>
       <c r="F98" t="n">
-        <v>703.8337944452578</v>
+        <v>703.9933324789404</v>
       </c>
       <c r="G98" t="n">
-        <v>-1.767788632901911</v>
+        <v>-1.745522333713835</v>
       </c>
       <c r="H98" t="n">
         <v>717.5</v>
       </c>
       <c r="I98" t="n">
-        <v>0.287970987548828</v>
+        <v>0.3219672296142577</v>
       </c>
       <c r="J98" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="K98" t="n">
-        <v>0.487665319424866</v>
+        <v>0.4901316365197205</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:17</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M98" t="n">
         <v>23702600</v>
       </c>
+      <c r="N98" t="n">
+        <v>40.95651123504027</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.05716191379628788</v>
+      </c>
+      <c r="P98" t="n">
+        <v>688.1478770131772</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>713.7603709126403</v>
+      </c>
+      <c r="R98" t="n">
+        <v>731.2689116642265</v>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5239,10 +6435,8 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C99" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="D99" t="n">
         <v>0.43</v>
@@ -5251,31 +6445,51 @@
         <v>191.1300048828125</v>
       </c>
       <c r="F99" t="n">
-        <v>189.2059735295701</v>
+        <v>189.1985323820706</v>
       </c>
       <c r="G99" t="n">
-        <v>-1.006661070522193</v>
+        <v>-1.01055430931746</v>
       </c>
       <c r="H99" t="n">
         <v>190</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3940490283203125</v>
+        <v>0.4406794213867187</v>
       </c>
       <c r="J99" t="n">
         <v>4.05</v>
       </c>
       <c r="K99" t="n">
-        <v>0.5756397816567489</v>
+        <v>0.5692915664187475</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:17</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M99" t="n">
         <v>178936900</v>
       </c>
+      <c r="N99" t="n">
+        <v>12.73584698115985</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.06663447211738723</v>
+      </c>
+      <c r="P99" t="n">
+        <v>184.4404003639672</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>191.1464968152866</v>
+      </c>
+      <c r="R99" t="n">
+        <v>196.9517743403094</v>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5288,10 +6502,8 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+      <c r="C100" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="D100" t="n">
         <v>1.71</v>
@@ -5300,31 +6512,51 @@
         <v>305.8900146484375</v>
       </c>
       <c r="F100" t="n">
-        <v>303.3763241158534</v>
+        <v>303.7517850432604</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.8217628599197899</v>
+        <v>-0.6990190927397707</v>
       </c>
       <c r="H100" t="n">
         <v>305</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2469557727050781</v>
+        <v>0.256294058227539</v>
       </c>
       <c r="J100" t="n">
         <v>5.83</v>
       </c>
       <c r="K100" t="n">
-        <v>0.5435924808142418</v>
+        <v>0.5426695973550159</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:17</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M100" t="n">
         <v>11951400</v>
       </c>
+      <c r="N100" t="n">
+        <v>24.30975669548293</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.07947221397018264</v>
+      </c>
+      <c r="P100" t="n">
+        <v>295.2501667778519</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>307.2581721147432</v>
+      </c>
+      <c r="R100" t="n">
+        <v>316.5643762508339</v>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5334,46 +6566,64 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SMR</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="D101" t="n">
         <v>1.71</v>
       </c>
       <c r="E101" t="n">
-        <v>17.47999954223633</v>
+        <v>321.8299865722656</v>
       </c>
       <c r="F101" t="n">
-        <v>18.59736006391511</v>
+        <v>324.1650767511039</v>
       </c>
       <c r="G101" t="n">
-        <v>6.39222283146486</v>
+        <v>0.7255663786052788</v>
       </c>
       <c r="H101" t="n">
-        <v>17.5</v>
+        <v>322.5</v>
       </c>
       <c r="I101" t="n">
-        <v>1.033207958984375</v>
+        <v>0.2464674963378906</v>
       </c>
       <c r="J101" t="n">
-        <v>1.43</v>
+        <v>5.3</v>
       </c>
       <c r="K101" t="n">
-        <v>0.5369810897019615</v>
+        <v>0.4991532496094539</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:17</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>25594700</v>
-      </c>
+        <v>11196300</v>
+      </c>
+      <c r="N101" t="n">
+        <v>21.12504799037034</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.06564039670562767</v>
+      </c>
+      <c r="P101" t="n">
+        <v>313.6412625096228</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>325.2501924557351</v>
+      </c>
+      <c r="R101" t="n">
+        <v>335.1578137028483</v>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5383,51 +6633,69 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="D102" t="n">
         <v>1.71</v>
       </c>
       <c r="E102" t="n">
-        <v>79.62000274658203</v>
+        <v>286.9299926757812</v>
       </c>
       <c r="F102" t="n">
-        <v>83.17402605553951</v>
+        <v>292.6487419857213</v>
       </c>
       <c r="G102" t="n">
-        <v>4.463731708562459</v>
+        <v>1.993081746738828</v>
       </c>
       <c r="H102" t="n">
-        <v>80</v>
+        <v>287.5</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9697268652343749</v>
+        <v>0.3436955279541015</v>
       </c>
       <c r="J102" t="n">
-        <v>6.05</v>
+        <v>6.61</v>
       </c>
       <c r="K102" t="n">
-        <v>0.5264884933011161</v>
+        <v>0.5060397689896073</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-01-31 21:43:17</t>
+          <t>2026-01-31 22:32:34</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>10707200</v>
-      </c>
+        <v>12002900</v>
+      </c>
+      <c r="N102" t="n">
+        <v>17.16753593639537</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.05983179303180746</v>
+      </c>
+      <c r="P102" t="n">
+        <v>283.0172068827531</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>291.6206482593037</v>
+      </c>
+      <c r="R102" t="n">
+        <v>300.1240496198479</v>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5435,48 +6703,66 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C103" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D103" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="E103" t="n">
-        <v>430.4100036621094</v>
+        <v>421.8099975585938</v>
       </c>
       <c r="F103" t="n">
-        <v>429.5682021212657</v>
+        <v>343.2209879886219</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.1955813140218104</v>
+        <v>-18.63137669207451</v>
       </c>
       <c r="H103" t="n">
-        <v>430</v>
+        <v>422.5</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4532525378417969</v>
+        <v>0.4674125524902344</v>
       </c>
       <c r="J103" t="n">
-        <v>8.15</v>
+        <v>7.95</v>
       </c>
       <c r="K103" t="n">
-        <v>0.5199709498559087</v>
+        <v>0.4953864406234577</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:27</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>82483000</v>
-      </c>
+        <v>55850125</v>
+      </c>
+      <c r="N103" t="n">
+        <v>35.00328329486904</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.08298353167887332</v>
+      </c>
+      <c r="P103" t="n">
+        <v>319.3130675088827</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>341.5159889459139</v>
+      </c>
+      <c r="R103" t="n">
+        <v>357.5180944861166</v>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5484,48 +6770,66 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C104" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D104" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="E104" t="n">
-        <v>259.4800109863281</v>
+        <v>270.010009765625</v>
       </c>
       <c r="F104" t="n">
-        <v>259.8603722016688</v>
+        <v>262.9824393974186</v>
       </c>
       <c r="G104" t="n">
-        <v>0.1465859408186541</v>
+        <v>-2.602707349370674</v>
       </c>
       <c r="H104" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="I104" t="n">
-        <v>0.286139951171875</v>
+        <v>0.2700268310546875</v>
       </c>
       <c r="J104" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="K104" t="n">
-        <v>0.4696438076487838</v>
+        <v>0.5095046732495393</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>92352600</v>
-      </c>
+        <v>72890096</v>
+      </c>
+      <c r="N104" t="n">
+        <v>23.75113257631966</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.08796389658641249</v>
+      </c>
+      <c r="P104" t="n">
+        <v>259.4361073215098</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>268.5402455661664</v>
+      </c>
+      <c r="R104" t="n">
+        <v>276.443838108231</v>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5533,48 +6837,66 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C105" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D105" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="E105" t="n">
-        <v>430.2900085449219</v>
+        <v>423.3699951171875</v>
       </c>
       <c r="F105" t="n">
-        <v>432.3455875944375</v>
+        <v>424.728075930668</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4777194470461525</v>
+        <v>0.3207787110904257</v>
       </c>
       <c r="H105" t="n">
-        <v>430</v>
+        <v>422.5</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2868723657226562</v>
+        <v>0.2917551293945311</v>
       </c>
       <c r="J105" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K105" t="n">
-        <v>0.5199819663635014</v>
+        <v>0.5399537178957512</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>58470400</v>
-      </c>
+        <v>41784456</v>
+      </c>
+      <c r="N105" t="n">
+        <v>21.57030366650014</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.05094906090482286</v>
+      </c>
+      <c r="P105" t="n">
+        <v>414.4375162379839</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>427.2408417770849</v>
+      </c>
+      <c r="R105" t="n">
+        <v>437.9436217199273</v>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5582,48 +6904,66 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C106" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D106" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="E106" t="n">
-        <v>239.3000030517578</v>
+        <v>242.9600067138672</v>
       </c>
       <c r="F106" t="n">
-        <v>232.9674621499871</v>
+        <v>243.5837378678704</v>
       </c>
       <c r="G106" t="n">
-        <v>-2.646276983289913</v>
+        <v>0.2567217388735871</v>
       </c>
       <c r="H106" t="n">
-        <v>240</v>
+        <v>242.5</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3295965478515624</v>
+        <v>0.8801281518554687</v>
       </c>
       <c r="J106" t="n">
-        <v>3.05</v>
+        <v>9.1</v>
       </c>
       <c r="K106" t="n">
-        <v>0.4598610613408551</v>
+        <v>0.5266045510830035</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>46535400</v>
-      </c>
+        <v>35407386</v>
+      </c>
+      <c r="N106" t="n">
+        <v>23.12566129598508</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.09518299578917966</v>
+      </c>
+      <c r="P106" t="n">
+        <v>230.5479763528877</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>245.4547521600728</v>
+      </c>
+      <c r="R106" t="n">
+        <v>258.8608458390178</v>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5631,48 +6971,66 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="C107" s="2" t="n">
+        <v>46062</v>
       </c>
       <c r="D107" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="E107" t="n">
-        <v>338</v>
+        <v>343.6900024414062</v>
       </c>
       <c r="F107" t="n">
-        <v>336.040497165381</v>
+        <v>344.3946165012032</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.5797345664553261</v>
+        <v>0.2050144184560972</v>
       </c>
       <c r="H107" t="n">
-        <v>337.5</v>
+        <v>342.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6051064880371095</v>
+        <v>0.5709271423339843</v>
       </c>
       <c r="J107" t="n">
-        <v>10.87</v>
+        <v>11.3</v>
       </c>
       <c r="K107" t="n">
-        <v>0.5240148979677688</v>
+        <v>0.5361425037300784</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>30980500</v>
-      </c>
+        <v>31667686</v>
+      </c>
+      <c r="N107" t="n">
+        <v>23.15828041164289</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.06738130363739926</v>
+      </c>
+      <c r="P107" t="n">
+        <v>326.5252621544328</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>342.8408007626311</v>
+      </c>
+      <c r="R107" t="n">
+        <v>360.6577693040991</v>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5680,48 +7038,66 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C108" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D108" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="E108" t="n">
-        <v>716.5</v>
+        <v>706.4099731445312</v>
       </c>
       <c r="F108" t="n">
-        <v>704.0144317539018</v>
+        <v>593.7643711379144</v>
       </c>
       <c r="G108" t="n">
-        <v>-1.742577564005329</v>
+        <v>-15.94620776730874</v>
       </c>
       <c r="H108" t="n">
-        <v>717.5</v>
+        <v>707.5</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3219672296142577</v>
+        <v>0.324652749633789</v>
       </c>
       <c r="J108" t="n">
-        <v>9.029999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="K108" t="n">
-        <v>0.4841638853542514</v>
+        <v>0.4883159957368852</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M108" t="n">
-        <v>23702600</v>
-      </c>
+        <v>14250265</v>
+      </c>
+      <c r="N108" t="n">
+        <v>62.69332761206709</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.08874921079184715</v>
+      </c>
+      <c r="P108" t="n">
+        <v>577.03293772503</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>603.1364181890918</v>
+      </c>
+      <c r="R108" t="n">
+        <v>627.7396986264835</v>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5729,48 +7105,66 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="C109" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="D109" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="E109" t="n">
-        <v>191.1300048828125</v>
+        <v>185.6100006103516</v>
       </c>
       <c r="F109" t="n">
-        <v>189.1972916728533</v>
+        <v>184.0954513343549</v>
       </c>
       <c r="G109" t="n">
-        <v>-1.01120345345262</v>
+        <v>-0.815984737361293</v>
       </c>
       <c r="H109" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4406794213867187</v>
+        <v>0.5185595019531251</v>
       </c>
       <c r="J109" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="K109" t="n">
-        <v>0.5804832740994962</v>
+        <v>0.5393405507193131</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M109" t="n">
-        <v>178936900</v>
-      </c>
+        <v>160114156</v>
+      </c>
+      <c r="N109" t="n">
+        <v>17.02206013569541</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.09170874457044791</v>
+      </c>
+      <c r="P109" t="n">
+        <v>177.829934590227</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>186.7333589842247</v>
+      </c>
+      <c r="R109" t="n">
+        <v>194.2362447095036</v>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5778,141 +7172,195 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+      <c r="C110" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="D110" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="E110" t="n">
-        <v>305.8900146484375</v>
+        <v>308.1400146484375</v>
       </c>
       <c r="F110" t="n">
-        <v>303.4935207492527</v>
+        <v>320.0421342173562</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.7834495355917777</v>
+        <v>3.862568638642434</v>
       </c>
       <c r="H110" t="n">
-        <v>305</v>
+        <v>307.5</v>
       </c>
       <c r="I110" t="n">
-        <v>0.256294058227539</v>
+        <v>0.2497633618164062</v>
       </c>
       <c r="J110" t="n">
-        <v>5.83</v>
+        <v>5.4</v>
       </c>
       <c r="K110" t="n">
-        <v>0.5430247220984498</v>
+        <v>0.5361922486264307</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M110" t="n">
-        <v>11951400</v>
-      </c>
+        <v>7980536</v>
+      </c>
+      <c r="N110" t="n">
+        <v>20.62641188230993</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.06693844000053994</v>
+      </c>
+      <c r="P110" t="n">
+        <v>307.3582388258839</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>315.5637091394263</v>
+      </c>
+      <c r="R110" t="n">
+        <v>324.869913275517</v>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SMR</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="D111" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="E111" t="n">
-        <v>17.47999954223633</v>
+        <v>333.8399963378906</v>
       </c>
       <c r="F111" t="n">
-        <v>18.59698525062723</v>
+        <v>341.5148638247951</v>
       </c>
       <c r="G111" t="n">
-        <v>6.390078590631338</v>
+        <v>2.298965843246801</v>
       </c>
       <c r="H111" t="n">
-        <v>17.5</v>
+        <v>335</v>
       </c>
       <c r="I111" t="n">
-        <v>1.072270263671875</v>
+        <v>0.2183916052246093</v>
       </c>
       <c r="J111" t="n">
-        <v>1.43</v>
+        <v>4.2</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5365663106650599</v>
+        <v>0.4780111587079128</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M111" t="n">
-        <v>25594700</v>
-      </c>
+        <v>8330077</v>
+      </c>
+      <c r="N111" t="n">
+        <v>13.81324569606551</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.04137684473877318</v>
+      </c>
+      <c r="P111" t="n">
+        <v>332.1142433234421</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>338.8241839762611</v>
+      </c>
+      <c r="R111" t="n">
+        <v>346.7359050445104</v>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="D112" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="E112" t="n">
-        <v>79.62000274658203</v>
+        <v>285.5899963378906</v>
       </c>
       <c r="F112" t="n">
-        <v>83.17257377262925</v>
+        <v>268.6673455634796</v>
       </c>
       <c r="G112" t="n">
-        <v>4.46190769090337</v>
+        <v>-5.925505441860555</v>
       </c>
       <c r="H112" t="n">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="I112" t="n">
-        <v>1.006352624511718</v>
+        <v>0.35938140625</v>
       </c>
       <c r="J112" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="K112" t="n">
-        <v>0.5260216696843615</v>
+        <v>0.5312152754055025</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-02-01 21:44:28</t>
+          <t>2026-02-02 20:41:40</t>
         </is>
       </c>
       <c r="M112" t="n">
-        <v>10707200</v>
-      </c>
+        <v>8585154</v>
+      </c>
+      <c r="N112" t="n">
+        <v>23.52837744919666</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.08238515967260804</v>
+      </c>
+      <c r="P112" t="n">
+        <v>254.4187650914108</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>272.3249396343567</v>
+      </c>
+      <c r="R112" t="n">
+        <v>283.8289065194895</v>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,11 +5503,17 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>421.8099975585938</v>
+      </c>
       <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
+      <c r="U83" t="b">
+        <v>1</v>
+      </c>
       <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="W83" t="n">
+        <v>0.9173664067405036</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5560,11 +5566,17 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>270.010009765625</v>
+      </c>
       <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="b">
+        <v>0</v>
+      </c>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="W84" t="n">
+        <v>4.653957032711853</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5617,11 +5629,17 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>423.3699951171875</v>
+      </c>
       <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
+      <c r="U85" t="b">
+        <v>1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="W85" t="n">
+        <v>1.457341326605152</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5674,11 +5692,17 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>242.9600067138672</v>
+      </c>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
+      <c r="U86" t="b">
+        <v>0</v>
+      </c>
       <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="W86" t="n">
+        <v>2.15878581970128</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5731,11 +5755,17 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>343.6900024414062</v>
+      </c>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
+      <c r="U87" t="b">
+        <v>1</v>
+      </c>
       <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="W87" t="n">
+        <v>1.615867389087445</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5788,11 +5818,17 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>706.4099731445312</v>
+      </c>
       <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
+      <c r="U88" t="b">
+        <v>0</v>
+      </c>
       <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="W88" t="n">
+        <v>1.937809128627035</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5845,11 +5881,17 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>185.6100006103516</v>
+      </c>
       <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
+      <c r="U89" t="b">
+        <v>1</v>
+      </c>
       <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="W89" t="n">
+        <v>0.6482400702057742</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7362,6 +7404,676 @@
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E113" t="n">
+        <v>421.9599914550781</v>
+      </c>
+      <c r="F113" t="n">
+        <v>418.0198056655523</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-0.9337818440887118</v>
+      </c>
+      <c r="H113" t="n">
+        <v>422.5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.4857229162597656</v>
+      </c>
+      <c r="J113" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.4862950409579886</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>55512048</v>
+      </c>
+      <c r="N113" t="n">
+        <v>25.96776164974949</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.06154081471137299</v>
+      </c>
+      <c r="P113" t="n">
+        <v>409.8173648354834</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>421.319031743731</v>
+      </c>
+      <c r="R113" t="n">
+        <v>432.2206116828526</v>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E114" t="n">
+        <v>269.4800109863281</v>
+      </c>
+      <c r="F114" t="n">
+        <v>268.040606335643</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-0.5341415288713687</v>
+      </c>
+      <c r="H114" t="n">
+        <v>270</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.2841868457031249</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.4535754663187671</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>63714867</v>
+      </c>
+      <c r="N114" t="n">
+        <v>13.64054952079035</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.05061803831335897</v>
+      </c>
+      <c r="P114" t="n">
+        <v>262.6313156578289</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>269.4347173586793</v>
+      </c>
+      <c r="R114" t="n">
+        <v>275.9379689844923</v>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E115" t="n">
+        <v>411.2099914550781</v>
+      </c>
+      <c r="F115" t="n">
+        <v>410.5726599290308</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-0.1549893094260924</v>
+      </c>
+      <c r="H115" t="n">
+        <v>410</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.358404853515625</v>
+      </c>
+      <c r="J115" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.5678270978706291</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>56864712</v>
+      </c>
+      <c r="N115" t="n">
+        <v>9.624918910412676</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.02340633523119083</v>
+      </c>
+      <c r="P115" t="n">
+        <v>405.0180387012135</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>411.1200393571663</v>
+      </c>
+      <c r="R115" t="n">
+        <v>416.1216792390948</v>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E116" t="n">
+        <v>238.6199951171875</v>
+      </c>
+      <c r="F116" t="n">
+        <v>239.8783330016008</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.5273396656450965</v>
+      </c>
+      <c r="H116" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.110111871337891</v>
+      </c>
+      <c r="J116" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.5443642456772768</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>50361798</v>
+      </c>
+      <c r="N116" t="n">
+        <v>24.41377504653918</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.1023123608503531</v>
+      </c>
+      <c r="P116" t="n">
+        <v>225.9419228892143</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>241.9497315763787</v>
+      </c>
+      <c r="R116" t="n">
+        <v>256.1566617862372</v>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E117" t="n">
+        <v>339.7099914550781</v>
+      </c>
+      <c r="F117" t="n">
+        <v>338.4804134741881</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-0.3619493131842664</v>
+      </c>
+      <c r="H117" t="n">
+        <v>340</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.642703768310547</v>
+      </c>
+      <c r="J117" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5103091511067032</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>35791301</v>
+      </c>
+      <c r="N117" t="n">
+        <v>26.3638100448135</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.07760681377633175</v>
+      </c>
+      <c r="P117" t="n">
+        <v>322.4410293066476</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>340.0536097212295</v>
+      </c>
+      <c r="R117" t="n">
+        <v>356.265189421015</v>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E118" t="n">
+        <v>691.7000122070312</v>
+      </c>
+      <c r="F118" t="n">
+        <v>609.2579252186807</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-11.91876326925305</v>
+      </c>
+      <c r="H118" t="n">
+        <v>692.5</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.3693300372314453</v>
+      </c>
+      <c r="J118" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4817049536746505</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>13473350</v>
+      </c>
+      <c r="N118" t="n">
+        <v>27.64320763235247</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.03996415663511459</v>
+      </c>
+      <c r="P118" t="n">
+        <v>594.8066935949221</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>606.6089632621658</v>
+      </c>
+      <c r="R118" t="n">
+        <v>618.2111944604732</v>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E119" t="n">
+        <v>180.3399963378906</v>
+      </c>
+      <c r="F119" t="n">
+        <v>180.1217776773555</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-0.1210040284830957</v>
+      </c>
+      <c r="H119" t="n">
+        <v>180</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.56055126953125</v>
+      </c>
+      <c r="J119" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5325924232666728</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>195713884</v>
+      </c>
+      <c r="N119" t="n">
+        <v>12.48168995192328</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.06921198960510788</v>
+      </c>
+      <c r="P119" t="n">
+        <v>173.625450180072</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>180.9283713485394</v>
+      </c>
+      <c r="R119" t="n">
+        <v>187.7310924369748</v>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E120" t="n">
+        <v>314.8500061035156</v>
+      </c>
+      <c r="F120" t="n">
+        <v>295.232920691006</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-6.230613000547295</v>
+      </c>
+      <c r="H120" t="n">
+        <v>315</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.2777171838378906</v>
+      </c>
+      <c r="J120" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.5099589178643622</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>11053267</v>
+      </c>
+      <c r="N120" t="n">
+        <v>26.83997959918859</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.08524687654083832</v>
+      </c>
+      <c r="P120" t="n">
+        <v>269.6196957566053</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>302.9463570856685</v>
+      </c>
+      <c r="R120" t="n">
+        <v>316.7574059247398</v>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E121" t="n">
+        <v>328.9299926757812</v>
+      </c>
+      <c r="F121" t="n">
+        <v>330.6075305437384</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.5099984511326424</v>
+      </c>
+      <c r="H121" t="n">
+        <v>330</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.2767406311035155</v>
+      </c>
+      <c r="J121" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.4829562602718913</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>9074864</v>
+      </c>
+      <c r="N121" t="n">
+        <v>15.74113623584828</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.04785558199724266</v>
+      </c>
+      <c r="P121" t="n">
+        <v>321.6348903717827</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>332.0448045757864</v>
+      </c>
+      <c r="R121" t="n">
+        <v>340.8531935176358</v>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E122" t="n">
+        <v>284.1799926757812</v>
+      </c>
+      <c r="F122" t="n">
+        <v>283.4014803161534</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.2739504467916656</v>
+      </c>
+      <c r="H122" t="n">
+        <v>285</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3433903552246094</v>
+      </c>
+      <c r="J122" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.4926898804564401</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:28:26</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>10643872</v>
+      </c>
+      <c r="N122" t="n">
+        <v>21.77668688588829</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.07662990867458128</v>
+      </c>
+      <c r="P122" t="n">
+        <v>273.0210985813023</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>285.325572935613</v>
+      </c>
+      <c r="R122" t="n">
+        <v>296.1295016369589</v>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sp500_options_analysis.xlsx
+++ b/sp500_options_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W122"/>
+  <dimension ref="A1:W132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5507,7 +5507,7 @@
         <v>421.8099975585938</v>
       </c>
       <c r="T83" t="inlineStr"/>
-      <c r="U83" t="b">
+      <c r="U83" t="n">
         <v>1</v>
       </c>
       <c r="V83" t="inlineStr"/>
@@ -5570,7 +5570,7 @@
         <v>270.010009765625</v>
       </c>
       <c r="T84" t="inlineStr"/>
-      <c r="U84" t="b">
+      <c r="U84" t="n">
         <v>0</v>
       </c>
       <c r="V84" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
         <v>423.3699951171875</v>
       </c>
       <c r="T85" t="inlineStr"/>
-      <c r="U85" t="b">
+      <c r="U85" t="n">
         <v>1</v>
       </c>
       <c r="V85" t="inlineStr"/>
@@ -5696,7 +5696,7 @@
         <v>242.9600067138672</v>
       </c>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="b">
+      <c r="U86" t="n">
         <v>0</v>
       </c>
       <c r="V86" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         <v>343.6900024414062</v>
       </c>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="b">
+      <c r="U87" t="n">
         <v>1</v>
       </c>
       <c r="V87" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
         <v>706.4099731445312</v>
       </c>
       <c r="T88" t="inlineStr"/>
-      <c r="U88" t="b">
+      <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="inlineStr"/>
@@ -5885,7 +5885,7 @@
         <v>185.6100006103516</v>
       </c>
       <c r="T89" t="inlineStr"/>
-      <c r="U89" t="b">
+      <c r="U89" t="n">
         <v>1</v>
       </c>
       <c r="V89" t="inlineStr"/>
@@ -8074,6 +8074,676 @@
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E123" t="n">
+        <v>421.9599914550781</v>
+      </c>
+      <c r="F123" t="n">
+        <v>418.0198056655523</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-0.9337818440887118</v>
+      </c>
+      <c r="H123" t="n">
+        <v>422.5</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.4857229162597656</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.4862950409579886</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>56752500</v>
+      </c>
+      <c r="N123" t="n">
+        <v>25.96776164974949</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.06154081471137299</v>
+      </c>
+      <c r="P123" t="n">
+        <v>409.8173648354834</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>421.319031743731</v>
+      </c>
+      <c r="R123" t="n">
+        <v>432.2206116828526</v>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E124" t="n">
+        <v>269.4800109863281</v>
+      </c>
+      <c r="F124" t="n">
+        <v>268.040606335643</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-0.5341415288713687</v>
+      </c>
+      <c r="H124" t="n">
+        <v>270</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.2841868457031249</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4535754663187671</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>64339600</v>
+      </c>
+      <c r="N124" t="n">
+        <v>13.64054952079035</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.05061803831335897</v>
+      </c>
+      <c r="P124" t="n">
+        <v>262.6313156578289</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>269.4347173586793</v>
+      </c>
+      <c r="R124" t="n">
+        <v>275.9379689844923</v>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E125" t="n">
+        <v>411.2099914550781</v>
+      </c>
+      <c r="F125" t="n">
+        <v>410.5726599290308</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-0.1549893094260924</v>
+      </c>
+      <c r="H125" t="n">
+        <v>410</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.358404853515625</v>
+      </c>
+      <c r="J125" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.5678270978706291</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>61301500</v>
+      </c>
+      <c r="N125" t="n">
+        <v>9.624918910412676</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.02340633523119083</v>
+      </c>
+      <c r="P125" t="n">
+        <v>405.0180387012135</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>411.1200393571663</v>
+      </c>
+      <c r="R125" t="n">
+        <v>416.1216792390948</v>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E126" t="n">
+        <v>238.6199951171875</v>
+      </c>
+      <c r="F126" t="n">
+        <v>239.8783330016008</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.5273396656450965</v>
+      </c>
+      <c r="H126" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.110111871337891</v>
+      </c>
+      <c r="J126" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.5443642456772768</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>53743900</v>
+      </c>
+      <c r="N126" t="n">
+        <v>24.41377504653918</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.1023123608503531</v>
+      </c>
+      <c r="P126" t="n">
+        <v>225.9419228892143</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>241.9497315763787</v>
+      </c>
+      <c r="R126" t="n">
+        <v>256.1566617862372</v>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E127" t="n">
+        <v>339.7099914550781</v>
+      </c>
+      <c r="F127" t="n">
+        <v>338.4804134741881</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-0.3619493131842664</v>
+      </c>
+      <c r="H127" t="n">
+        <v>340</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.642703768310547</v>
+      </c>
+      <c r="J127" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.5103091511067032</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>36406300</v>
+      </c>
+      <c r="N127" t="n">
+        <v>26.3638100448135</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.07760681377633175</v>
+      </c>
+      <c r="P127" t="n">
+        <v>322.4410293066476</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>340.0536097212295</v>
+      </c>
+      <c r="R127" t="n">
+        <v>356.265189421015</v>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E128" t="n">
+        <v>691.7000122070312</v>
+      </c>
+      <c r="F128" t="n">
+        <v>609.2579252186807</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-11.91876326925305</v>
+      </c>
+      <c r="H128" t="n">
+        <v>692.5</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3693300372314453</v>
+      </c>
+      <c r="J128" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.4817049536746505</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
+        <v>13733000</v>
+      </c>
+      <c r="N128" t="n">
+        <v>27.64320763235247</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.03996415663511459</v>
+      </c>
+      <c r="P128" t="n">
+        <v>594.8066935949221</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>606.6089632621658</v>
+      </c>
+      <c r="R128" t="n">
+        <v>618.2111944604732</v>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E129" t="n">
+        <v>180.3399963378906</v>
+      </c>
+      <c r="F129" t="n">
+        <v>180.1217776773555</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-0.1210040284830957</v>
+      </c>
+      <c r="H129" t="n">
+        <v>180</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.56055126953125</v>
+      </c>
+      <c r="J129" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.5325924232666728</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
+        <v>203461100</v>
+      </c>
+      <c r="N129" t="n">
+        <v>12.48168995192328</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.06921198960510788</v>
+      </c>
+      <c r="P129" t="n">
+        <v>173.625450180072</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>180.9283713485394</v>
+      </c>
+      <c r="R129" t="n">
+        <v>187.7310924369748</v>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E130" t="n">
+        <v>314.8500061035156</v>
+      </c>
+      <c r="F130" t="n">
+        <v>295.232920691006</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-6.230613000547295</v>
+      </c>
+      <c r="H130" t="n">
+        <v>315</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2777171838378906</v>
+      </c>
+      <c r="J130" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.5099589178643622</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>12685800</v>
+      </c>
+      <c r="N130" t="n">
+        <v>26.83997959918859</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.08524687654083832</v>
+      </c>
+      <c r="P130" t="n">
+        <v>269.6196957566053</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>302.9463570856685</v>
+      </c>
+      <c r="R130" t="n">
+        <v>316.7574059247398</v>
+      </c>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E131" t="n">
+        <v>328.9299926757812</v>
+      </c>
+      <c r="F131" t="n">
+        <v>330.6075305437384</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.5099984511326424</v>
+      </c>
+      <c r="H131" t="n">
+        <v>330</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.2767406311035155</v>
+      </c>
+      <c r="J131" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.4829562602718913</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>9078500</v>
+      </c>
+      <c r="N131" t="n">
+        <v>15.74113623584828</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.04785558199724266</v>
+      </c>
+      <c r="P131" t="n">
+        <v>321.6348903717827</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>332.0448045757864</v>
+      </c>
+      <c r="R131" t="n">
+        <v>340.8531935176358</v>
+      </c>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E132" t="n">
+        <v>284.1799926757812</v>
+      </c>
+      <c r="F132" t="n">
+        <v>283.4014803161534</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-0.2739504467916656</v>
+      </c>
+      <c r="H132" t="n">
+        <v>285</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3433903552246094</v>
+      </c>
+      <c r="J132" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.4926898804564401</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-02-04 02:34:38</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>10794000</v>
+      </c>
+      <c r="N132" t="n">
+        <v>21.77668688588829</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.07662990867458128</v>
+      </c>
+      <c r="P132" t="n">
+        <v>273.0210985813023</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>285.325572935613</v>
+      </c>
+      <c r="R132" t="n">
+        <v>296.1295016369589</v>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
